--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136320476</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136320480</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136320478</v>
       </c>
       <c r="B4" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136320492</v>
       </c>
       <c r="B5" t="n">
-        <v>93397</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136320473</v>
       </c>
       <c r="B6" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136320487</v>
       </c>
       <c r="B7" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136320479</v>
       </c>
       <c r="B8" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>136320474</v>
       </c>
       <c r="B9" t="n">
-        <v>93376</v>
+        <v>93382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136320475</v>
       </c>
       <c r="B10" t="n">
-        <v>93376</v>
+        <v>93382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136320491</v>
       </c>
       <c r="B11" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136320494</v>
       </c>
       <c r="B12" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>136320490</v>
       </c>
       <c r="B13" t="n">
-        <v>93403</v>
+        <v>93409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136320476</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136320480</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136320478</v>
       </c>
       <c r="B4" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136320492</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136320473</v>
       </c>
       <c r="B6" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136320487</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136320479</v>
       </c>
       <c r="B8" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>136320474</v>
       </c>
       <c r="B9" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136320475</v>
       </c>
       <c r="B10" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136320491</v>
       </c>
       <c r="B11" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136320494</v>
       </c>
       <c r="B12" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>136320490</v>
       </c>
       <c r="B13" t="n">
-        <v>93409</v>
+        <v>93416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136320478</v>
       </c>
       <c r="B4" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136320492</v>
       </c>
       <c r="B5" t="n">
-        <v>93410</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136320473</v>
       </c>
       <c r="B6" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136320487</v>
       </c>
       <c r="B7" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136320479</v>
       </c>
       <c r="B8" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>136320474</v>
       </c>
       <c r="B9" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136320475</v>
       </c>
       <c r="B10" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>136320490</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136320476</v>
       </c>
       <c r="B2" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136320480</v>
       </c>
       <c r="B3" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136320478</v>
       </c>
       <c r="B4" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136320492</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136320473</v>
+        <v>136453571</v>
       </c>
       <c r="B6" t="n">
-        <v>93380</v>
+        <v>93424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>688625</v>
+        <v>688587</v>
       </c>
       <c r="R6" t="n">
-        <v>7412539</v>
+        <v>7412438</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,19 +1200,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,7 +1217,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1238,16 +1228,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320473</t>
+          <t>https://artportalen.se/Sighting/136453571</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136320487</v>
+        <v>136453573</v>
       </c>
       <c r="B7" t="n">
-        <v>93380</v>
+        <v>93424</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,52 +1245,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688612</v>
+        <v>688622</v>
       </c>
       <c r="R7" t="n">
-        <v>7412681</v>
+        <v>7412463</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,35 +1302,24 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1366,16 +1330,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320487</t>
+          <t>https://artportalen.se/Sighting/136453573</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136320479</v>
+        <v>136453553</v>
       </c>
       <c r="B8" t="n">
-        <v>93386</v>
+        <v>92023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688599</v>
+        <v>688682</v>
       </c>
       <c r="R8" t="n">
-        <v>7412694</v>
+        <v>7412631</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,19 +1404,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,7 +1421,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1478,38 +1432,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320479</t>
+          <t>https://artportalen.se/Sighting/136453553</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136320474</v>
+        <v>136453598</v>
       </c>
       <c r="B9" t="n">
-        <v>93390</v>
+        <v>87496</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>3690</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>688598</v>
+        <v>688374</v>
       </c>
       <c r="R9" t="n">
-        <v>7412630</v>
+        <v>7412855</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,19 +1506,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,7 +1523,7 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1590,38 +1534,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320474</t>
+          <t>https://artportalen.se/Sighting/136453598</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136320475</v>
+        <v>136453638</v>
       </c>
       <c r="B10" t="n">
-        <v>93390</v>
+        <v>87496</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>3690</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,13 +1575,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>688611</v>
+        <v>688627</v>
       </c>
       <c r="R10" t="n">
-        <v>7412650</v>
+        <v>7412451</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,19 +1608,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,7 +1625,7 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1702,16 +1636,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320475</t>
+          <t>https://artportalen.se/Sighting/136453638</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136320491</v>
+        <v>136453639</v>
       </c>
       <c r="B11" t="n">
-        <v>80079</v>
+        <v>87496</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>688424</v>
+        <v>688586</v>
       </c>
       <c r="R11" t="n">
-        <v>7412719</v>
+        <v>7412433</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1776,19 +1710,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1727,7 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -1814,16 +1738,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320491</t>
+          <t>https://artportalen.se/Sighting/136453639</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136320494</v>
+        <v>136320473</v>
       </c>
       <c r="B12" t="n">
-        <v>80079</v>
+        <v>93393</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,40 +1755,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>688487</v>
+        <v>688625</v>
       </c>
       <c r="R12" t="n">
-        <v>7412652</v>
+        <v>7412539</v>
       </c>
       <c r="S12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1893,7 +1814,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,7 +1824,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,7 +1833,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1930,54 +1850,69 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320494</t>
+          <t>https://artportalen.se/Sighting/136320473</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136320490</v>
+        <v>136320487</v>
       </c>
       <c r="B13" t="n">
-        <v>93417</v>
+        <v>93393</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>688440</v>
+        <v>688612</v>
       </c>
       <c r="R13" t="n">
-        <v>7412736</v>
+        <v>7412681</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2006,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +1951,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,6 +1960,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2041,6 +1977,2018 @@
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320487</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136320479</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93399</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>688599</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7412694</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320479</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136453644</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93399</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>688371</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7412621</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453644</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136453645</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93399</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>688395</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7412641</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453645</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136453651</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93399</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>688743</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7412560</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453651</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136320474</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93403</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>688598</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7412630</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320474</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136320475</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93403</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>688611</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7412650</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320475</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136453604</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>688416</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7412828</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453604</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136453632</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90700</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>688397</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7412673</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453632</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136453633</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90700</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>688430</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7412788</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453633</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136453634</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90700</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>688382</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7412847</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453634</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136453630</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93425</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>688639</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7412502</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453630</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136320491</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80092</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>688424</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7412719</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320491</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136320494</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80092</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>688487</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7412652</v>
+      </c>
+      <c r="S26" t="n">
+        <v>16</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320494</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136453565</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57193</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>688428</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7412790</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453565</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136453569</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>688576</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7412433</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453569</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136453620</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98209</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>688698</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7412629</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453620</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136453623</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98209</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>688725</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7412597</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453623</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136453624</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98209</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>688670</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7412524</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453624</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136320490</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93430</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>688440</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7412736</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136320490</t>
         </is>
@@ -2060,6 +4008,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136320476</v>
       </c>
       <c r="B2" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136320480</v>
       </c>
       <c r="B3" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136320478</v>
       </c>
       <c r="B4" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136320492</v>
       </c>
       <c r="B5" t="n">
-        <v>93424</v>
+        <v>93425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136453571</v>
       </c>
       <c r="B6" t="n">
-        <v>93424</v>
+        <v>93425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453573</v>
       </c>
       <c r="B7" t="n">
-        <v>93424</v>
+        <v>93425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136453553</v>
       </c>
       <c r="B8" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136453598</v>
       </c>
       <c r="B9" t="n">
-        <v>87496</v>
+        <v>87497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136453638</v>
       </c>
       <c r="B10" t="n">
-        <v>87496</v>
+        <v>87497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136453639</v>
       </c>
       <c r="B11" t="n">
-        <v>87496</v>
+        <v>87497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136320473</v>
       </c>
       <c r="B12" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136320487</v>
       </c>
       <c r="B13" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136320479</v>
       </c>
       <c r="B14" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>136453644</v>
       </c>
       <c r="B15" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>136453645</v>
       </c>
       <c r="B16" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136453651</v>
       </c>
       <c r="B17" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136320474</v>
       </c>
       <c r="B18" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136320475</v>
       </c>
       <c r="B19" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136453604</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136453632</v>
       </c>
       <c r="B21" t="n">
-        <v>90700</v>
+        <v>90701</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136453633</v>
       </c>
       <c r="B22" t="n">
-        <v>90700</v>
+        <v>90701</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>136453634</v>
       </c>
       <c r="B23" t="n">
-        <v>90700</v>
+        <v>90701</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136453630</v>
       </c>
       <c r="B24" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136320491</v>
       </c>
       <c r="B25" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>136320494</v>
       </c>
       <c r="B26" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136453620</v>
       </c>
       <c r="B29" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136453623</v>
       </c>
       <c r="B30" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136453624</v>
       </c>
       <c r="B31" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>136320490</v>
       </c>
       <c r="B32" t="n">
-        <v>93430</v>
+        <v>93431</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
